--- a/data/trans_orig/P24B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78030</t>
+          <t>77775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96687</t>
+          <t>96741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127369</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150811</t>
+          <t>150911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21157</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>37222</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>72396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106794</t>
+          <t>105547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135800</t>
+          <t>133807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76632</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168852</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>205227</t>
+          <t>204321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>47182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41958</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52908</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82123</t>
+          <t>80970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113057</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61715</t>
+          <t>62787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141021</t>
+          <t>140553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170376</t>
+          <t>169483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31446</t>
+          <t>31784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>53447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34516</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61070</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>91824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118538</t>
+          <t>117494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52376</t>
+          <t>52020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72487</t>
+          <t>72737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150300</t>
+          <t>152966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>184639</t>
+          <t>184134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>48858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>46557</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75492</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71257</t>
+          <t>70985</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95469</t>
+          <t>95508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116634</t>
+          <t>115826</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83374</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101482</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>119109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142820</t>
+          <t>143038</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25785</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>46748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>62106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39514</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>62586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147481</t>
+          <t>146657</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175515</t>
+          <t>175137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73602</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98950</t>
+          <t>98629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229726</t>
+          <t>228692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267528</t>
+          <t>267342</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>35156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>35072</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>58793</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56841</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87693</t>
+          <t>86151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>55849</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27960</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64694</t>
+          <t>63335</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97075</t>
+          <t>95537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>220888</t>
+          <t>219693</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>250297</t>
+          <t>249382</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>113230</t>
+          <t>114144</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>138119</t>
+          <t>139254</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>343070</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>381393</t>
+          <t>382904</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>45544</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>189440</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>243889</t>
+          <t>242929</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>138394</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>185240</t>
+          <t>184899</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>413113</t>
+          <t>412919</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>940124</t>
+          <t>939685</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1007518</t>
+          <t>1008922</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>500371</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>557430</t>
+          <t>555900</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1456691</t>
+          <t>1455238</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1544929</t>
+          <t>1549496</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>217492</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>155027</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>200007</t>
+          <t>200549</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>335468</t>
+          <t>335610</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>405865</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64186</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95064</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66402</t>
+          <t>66746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28241</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78083</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109649</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42901</t>
+          <t>42716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49799</t>
+          <t>49353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79857</t>
+          <t>78731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>62393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91007</t>
+          <t>91771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59888</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104826</t>
+          <t>104438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143019</t>
+          <t>142428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74146</t>
+          <t>73767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>104452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54966</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79963</t>
+          <t>80289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136053</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176611</t>
+          <t>177622</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31042</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>55007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>27340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64346</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>95813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>53972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>34609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>54782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82162</t>
+          <t>82200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50342</t>
+          <t>50920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>74442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49558</t>
+          <t>50961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89470</t>
+          <t>88673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118611</t>
+          <t>119243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56758</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43243</t>
+          <t>43303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>58045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>87591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85146</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108930</t>
+          <t>106724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139792</t>
+          <t>137819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>27547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28056</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>52895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43266</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35823</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>58796</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44378</t>
+          <t>44175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73463</t>
+          <t>73215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>98671</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42865</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>39210</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>59603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84330</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37941</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59648</t>
+          <t>58370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90906</t>
+          <t>87926</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54431</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82375</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120399</t>
+          <t>121674</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162964</t>
+          <t>164043</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>148043</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>182839</t>
+          <t>182829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77512</t>
+          <t>79195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>106813</t>
+          <t>106439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>236530</t>
+          <t>233722</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>281647</t>
+          <t>281382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55069</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>56563</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92356</t>
+          <t>90894</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43651</t>
+          <t>43610</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72534</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67708</t>
+          <t>65115</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>100473</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>179048</t>
+          <t>178078</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>213182</t>
+          <t>212729</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>136383</t>
+          <t>135486</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>164512</t>
+          <t>164226</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>325333</t>
+          <t>325695</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>369897</t>
+          <t>369650</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31586</t>
+          <t>30543</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>44094</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>91856</t>
+          <t>93544</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>367083</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>443939</t>
+          <t>439573</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>229081</t>
+          <t>229976</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>286122</t>
+          <t>286682</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>621589</t>
+          <t>618292</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>709990</t>
+          <t>712119</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>692007</t>
+          <t>694759</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>769000</t>
+          <t>774568</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>480057</t>
+          <t>477272</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>546715</t>
+          <t>543528</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1191731</t>
+          <t>1191545</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1289279</t>
+          <t>1288048</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>191076</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>245250</t>
+          <t>247602</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>181764</t>
+          <t>182084</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>234812</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>383356</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>464289</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50169</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76386</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>31860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>39402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59369</t>
+          <t>58856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86095</t>
+          <t>86145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22726</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>48624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76472</t>
+          <t>78587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144160</t>
+          <t>142942</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170023</t>
+          <t>168587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84422</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107175</t>
+          <t>107028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236802</t>
+          <t>234981</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>271500</t>
+          <t>269000</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>68461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84057</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>54008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70050</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127780</t>
+          <t>128494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150100</t>
+          <t>149942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57001</t>
+          <t>55957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>64873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95521</t>
+          <t>97043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69891</t>
+          <t>70796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94070</t>
+          <t>95125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42590</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119787</t>
+          <t>119237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152048</t>
+          <t>152449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61007</t>
+          <t>60989</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74791</t>
+          <t>74803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37421</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102750</t>
+          <t>103307</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>120936</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64551</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98222</t>
+          <t>100024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121943</t>
+          <t>122671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>41949</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44863</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73219</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34729</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57552</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124611</t>
+          <t>121506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105481</t>
+          <t>105269</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>134281</t>
+          <t>135182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92211</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>203802</t>
+          <t>207686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243196</t>
+          <t>246649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51288</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38702</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65958</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50260</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>105039</t>
+          <t>105962</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>155280</t>
+          <t>152551</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>184761</t>
+          <t>183821</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>133498</t>
+          <t>133285</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>160458</t>
+          <t>161687</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>298285</t>
+          <t>296636</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>336552</t>
+          <t>339743</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46312</t>
+          <t>48862</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39662</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>79874</t>
+          <t>79938</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>230964</t>
+          <t>229114</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>289075</t>
+          <t>286366</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>175320</t>
+          <t>175165</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>225064</t>
+          <t>223493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>417022</t>
+          <t>418432</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>493559</t>
+          <t>495660</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>740385</t>
+          <t>740944</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>807654</t>
+          <t>807270</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>568218</t>
+          <t>566155</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>623617</t>
+          <t>624421</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1321097</t>
+          <t>1324660</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1408880</t>
+          <t>1411452</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>116593</t>
+          <t>118020</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>163319</t>
+          <t>162662</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>142982</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>233676</t>
+          <t>232895</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>295304</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>78535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96741</t>
+          <t>96615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>69,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>51024</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58368</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>59,01%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>139535</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>127384</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>152169</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>68,61%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51024</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42820</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58873</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>139535</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>126279</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>150911</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>75,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>68,01%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>35362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47764</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72396</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105547</t>
+          <t>108607</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133807</t>
+          <t>135985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>55302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76342</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>169899</t>
+          <t>170927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>204321</t>
+          <t>205915</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22605</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80970</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>33829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35901</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>91805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114357</t>
+          <t>114343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>42536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62787</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140553</t>
+          <t>140306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169483</t>
+          <t>170191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31784</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>29230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53447</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40296</t>
+          <t>39449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>28005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>61390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91824</t>
+          <t>91835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117494</t>
+          <t>117564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72737</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152966</t>
+          <t>151412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>184134</t>
+          <t>183738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74116</t>
+          <t>75019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>32672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70985</t>
+          <t>70690</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>50168</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95508</t>
+          <t>95530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115826</t>
+          <t>117458</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>101949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45519</t>
+          <t>45956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119109</t>
+          <t>118050</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143038</t>
+          <t>142388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46748</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62106</t>
+          <t>60960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62586</t>
+          <t>62723</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>146657</t>
+          <t>149059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175137</t>
+          <t>177517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98629</t>
+          <t>99426</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>228692</t>
+          <t>229446</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267342</t>
+          <t>268783</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35072</t>
+          <t>34364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58793</t>
+          <t>58072</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>86151</t>
+          <t>86726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>54412</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27787</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50178</t>
+          <t>49661</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>63335</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95537</t>
+          <t>96836</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>219693</t>
+          <t>220280</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>249382</t>
+          <t>251424</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>114144</t>
+          <t>112729</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>139254</t>
+          <t>138408</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>339721</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>382904</t>
+          <t>382361</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>47547</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>189440</t>
+          <t>188031</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>242929</t>
+          <t>242758</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138394</t>
+          <t>138517</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>184218</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>340076</t>
+          <t>344624</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>416003</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>940290</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1008922</t>
+          <t>1011181</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>499663</t>
+          <t>498398</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>555900</t>
+          <t>553817</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1455238</t>
+          <t>1457953</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1549496</t>
+          <t>1542820</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>164819</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>155027</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>200549</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>335610</t>
+          <t>334350</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>405865</t>
+          <t>404758</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63724</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>64402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92577</t>
+          <t>94378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43333</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66746</t>
+          <t>66145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28433</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>49001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>78931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>110611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49353</t>
+          <t>49138</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78731</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62393</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91771</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>59503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104438</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142428</t>
+          <t>141197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73767</t>
+          <t>75375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104452</t>
+          <t>104219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>137802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>177804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>54640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>63466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95813</t>
+          <t>96258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53972</t>
+          <t>53198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34609</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54782</t>
+          <t>55150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82200</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50920</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>72963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88673</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119243</t>
+          <t>117910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>33053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57503</t>
+          <t>56644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>51658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>43124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58045</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87591</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>84717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60386</t>
+          <t>60003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106724</t>
+          <t>106803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137819</t>
+          <t>138712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27547</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>28112</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52895</t>
+          <t>52655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58796</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>39772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>44703</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73215</t>
+          <t>72552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98671</t>
+          <t>98826</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39210</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>61667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>47413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41965</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59603</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85397</t>
+          <t>83894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87926</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>53731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>81109</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>121674</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>164043</t>
+          <t>163574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>150677</t>
+          <t>149844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>182829</t>
+          <t>184663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79195</t>
+          <t>79544</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>106439</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233722</t>
+          <t>236323</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>281382</t>
+          <t>282116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>53247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56563</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90894</t>
+          <t>90493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43610</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>73073</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>100473</t>
+          <t>101262</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178078</t>
+          <t>180191</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>212729</t>
+          <t>213536</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>137431</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>164226</t>
+          <t>164304</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>325695</t>
+          <t>325458</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>369650</t>
+          <t>371859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>30916</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56741</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>93544</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>367083</t>
+          <t>369359</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>439573</t>
+          <t>445012</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>229976</t>
+          <t>229875</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>286682</t>
+          <t>286355</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>618292</t>
+          <t>624268</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>712119</t>
+          <t>709832</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>694759</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>774568</t>
+          <t>769989</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>477272</t>
+          <t>479688</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>543528</t>
+          <t>545286</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1191545</t>
+          <t>1191531</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1288048</t>
+          <t>1289185</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>189889</t>
+          <t>188328</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>247602</t>
+          <t>245552</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>182084</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>234812</t>
+          <t>232260</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>387055</t>
+          <t>387386</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>464289</t>
+          <t>461151</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>49926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>50219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77260</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52619</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39402</t>
+          <t>38797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58856</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86145</t>
+          <t>86465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>55926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45977</t>
+          <t>44945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>48461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78587</t>
+          <t>76913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142942</t>
+          <t>142398</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168587</t>
+          <t>168155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107028</t>
+          <t>107194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>234981</t>
+          <t>237382</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>269000</t>
+          <t>269597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46693</t>
+          <t>44727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33860</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68461</t>
+          <t>68668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>55162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128494</t>
+          <t>128357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149942</t>
+          <t>149675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64873</t>
+          <t>64996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97043</t>
+          <t>96616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70796</t>
+          <t>70850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95125</t>
+          <t>95395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>64061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119237</t>
+          <t>119842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152449</t>
+          <t>151787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44502</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60989</t>
+          <t>61271</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74803</t>
+          <t>75556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49274</t>
+          <t>49346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103307</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120936</t>
+          <t>121377</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26593</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45741</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>48655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62037</t>
+          <t>62363</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100024</t>
+          <t>98205</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122671</t>
+          <t>121338</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>17447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41949</t>
+          <t>42649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58766</t>
+          <t>58560</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>85719</t>
+          <t>86997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>123065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105269</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135182</t>
+          <t>136214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90785</t>
+          <t>90863</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116553</t>
+          <t>117363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207686</t>
+          <t>206105</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246649</t>
+          <t>245029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28082</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52423</t>
+          <t>50572</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65123</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>49222</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70861</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>105962</t>
+          <t>105857</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>153888</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>183821</t>
+          <t>183686</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>133285</t>
+          <t>133135</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>161687</t>
+          <t>159583</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>296636</t>
+          <t>294944</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>339743</t>
+          <t>336715</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48862</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>46945</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>79938</t>
+          <t>80322</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>229114</t>
+          <t>229356</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>286366</t>
+          <t>287286</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>174032</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>223493</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>420110</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>495660</t>
+          <t>495334</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>740944</t>
+          <t>741170</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>807270</t>
+          <t>806208</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>566155</t>
+          <t>568299</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>624421</t>
+          <t>627045</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1324660</t>
+          <t>1325833</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1411452</t>
+          <t>1410439</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118020</t>
+          <t>118603</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>145935</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>232895</t>
+          <t>231646</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>295610</t>
+          <t>292687</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
